--- a/tests/data/templates/template_은행.xlsx
+++ b/tests/data/templates/template_은행.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bagja\OneDrive\바탕 화면\OCR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E65E4E1F-6DFA-4F9A-B36F-01B550A6257D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2C5CE1-F123-4FA8-A93B-0ADDDDA8E7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{712F3467-0943-4115-A9B8-64DF9599F99D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{712F3467-0943-4115-A9B8-64DF9599F99D}"/>
   </bookViews>
   <sheets>
     <sheet name="1.금융상품" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>금융상품의 종류</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -548,7 +548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9C6926-125D-45FE-ABDA-E3F1B77D0C0C}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -557,7 +557,7 @@
     <col min="9" max="9" width="21.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -584,6 +584,9 @@
       </c>
       <c r="I1" t="s">
         <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
